--- a/main/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/main/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T13:10:34+00:00</t>
+    <t>2026-05-22T13:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/main/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T13:20:51+00:00</t>
+    <t>2026-05-26T09:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
